--- a/data/processed/shopee_clean.xlsx
+++ b/data/processed/shopee_clean.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost Strong Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Strong Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost Strong Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Strong Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost Strong Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Strong Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M18" t="n">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Nordic Spirit Lush Red Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Lush Red Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -15617,7 +15617,7 @@
       <c r="K79" s="3" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M79" t="n">
@@ -18333,7 +18333,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M93" t="n">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M96" t="n">
@@ -20263,7 +20263,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M103" t="n">
@@ -20848,7 +20848,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M106" t="n">
@@ -21433,7 +21433,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M109" t="n">
@@ -22213,7 +22213,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M113" t="n">
@@ -22408,7 +22408,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M114" t="n">
@@ -23773,7 +23773,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M121" t="n">
@@ -24748,7 +24748,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Nordic Spirit Lush Red Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Lush Red Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M127" t="n">
@@ -25337,7 +25337,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M129" t="n">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M130" t="n">
@@ -25727,7 +25727,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M131" t="n">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M139" t="n">
@@ -27661,7 +27661,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M141" t="n">
@@ -28051,7 +28051,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M143" t="n">
@@ -30371,7 +30371,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M155" t="n">
@@ -30761,7 +30761,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Nordic Spirit Amber Roast Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Amber Roast Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M157" t="n">
@@ -30956,7 +30956,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M158" t="n">
@@ -31346,7 +31346,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M160" t="n">
@@ -32516,7 +32516,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Nordic Spirit Pink Citrine Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Pink Citrine Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M166" t="n">
@@ -33491,7 +33491,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M171" t="n">
@@ -34271,7 +34271,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M175" t="n">
@@ -34661,7 +34661,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M177" t="n">
@@ -36605,7 +36605,7 @@
       <c r="K187" s="3" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M187" t="n">
@@ -36786,7 +36786,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M188" t="n">
@@ -37371,7 +37371,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M191" t="n">
@@ -37566,7 +37566,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M192" t="n">
@@ -39468,7 +39468,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M202" t="n">
@@ -39663,7 +39663,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M203" t="n">
@@ -40638,7 +40638,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Amber Roast Strong Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M208" t="n">
@@ -41418,7 +41418,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M212" t="n">
@@ -42588,7 +42588,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M218" t="n">
@@ -52835,7 +52835,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>Nordic Spirit Pink Citrine Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Pink Citrine Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M271" t="n">
@@ -81352,7 +81352,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>Nordic Spirit Amber Roast Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Amber Roast Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M418" t="n">
@@ -85252,7 +85252,7 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>Nordic Spirit Lush Red Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Lush Red Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M438" t="n">
@@ -87982,7 +87982,7 @@
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>Nordic Spirit Lush Red Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Lush Red Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M452" t="n">
@@ -88762,7 +88762,7 @@
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M456" t="n">
@@ -89347,7 +89347,7 @@
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>Nordic Spirit Fresh Frost  Nicotine Pouch  (5-Can Bundle)</t>
+          <t>Nordic Spirit Fresh Frost Nicotine Pouch (5-Can Bundle)</t>
         </is>
       </c>
       <c r="M459" t="n">
